--- a/test.xlsx
+++ b/test.xlsx
@@ -15,12 +15,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2">
-  <si>
-    <t>Картинки</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+  <si>
+    <t>ссылка</t>
+  </si>
+  <si>
+    <t>картинки</t>
+  </si>
+  <si>
+    <t>совместимость</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/ECM-Ersatzteile/Pumpe-und-Fluidsystem/Anschluss-T-Form-1-8-fuer-Espressomaschine::20013.html</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/images/product_images/popup_images/anschluss-t-form-1-8-fuer-espressomaschine-15455.jpg|https://www.juraprofi.de/images/product_images/popup_images/anschluss-t-form-1-8-fuer-espressomaschine-15455-1.jpg</t>
+  </si>
+  <si>
+    <t>Barista,Casa IV,Casa V,Classika II,Classika PID,Compact HX-2,Controvento,Controvento Due,Elektronika II Profi,Elektronika Profi Due,Mechanika III,Mechanika IV,Mechanika Profi,Mechanika V Slim,Synchronika,Technika III,Technika IV,Technika Profi,Technika V Profi PID,Pro 300,Pro 500,Pro 600,Pro 700,Pro 800,0960 Carola (Einkreis),0975 La Certa (Einkreis),0980 Andreja,0980 Andreja (NEW),0980 Milano,0981 Rubino,0985 Aquila (NEW),0987 Rapida (Hebelmaschine),0990 Anita,0992 QM 67,0995 Vetrano,0995 Vetrano (NEW),0996 Achille (Hebelmaschine),04005 Silvano,04100 Pippa,Appartamento,Cellini,Cellini,Cinquantotto,Giotto,Mozzafiato,R58,R60</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/DeLonghi-Ersatzteile/Wassertank/Abdeckung-Wassertank-silber-fuer-DeLonghi-Perfecta-Evo::17096.html</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/images/product_images/popup_images/abdeckung-wassertank-silber-fuer-delonghi-perfecta-evo-5513237481.jpg|https://www.juraprofi.de/images/product_images/popup_images/abdeckung-wassertank-silber-fuer-delonghi-perfecta-evo-5513237481-1.jpg</t>
+  </si>
+  <si>
+    <t>ESAM 428.80.SB Perfecta Evo</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/ECM-Ersatzteile/Dichtungen/Teflondichtung-Dampfkessel-ECM-und-Profitec-Espressomaschine::19247.html</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/images/product_images/popup_images/teflondichtung-dampfkessel-ecm-und-profitec-espressomaschine-c469900779.jpg|https://www.juraprofi.de/images/product_images/popup_images/teflondichtung-dampfkessel-ecm-und-profitec-espressomaschine-c469900779-1.jpg</t>
+  </si>
+  <si>
+    <t>Compact HX-2,Controvento Due,Pro 800</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/ECM-Ersatzteile/Kaffeemuehle/Dosier-Einstellregler-fuer-ECM-Casa-Speciale-Kaffeemuehle::18825.html</t>
+  </si>
+  <si>
+    <t>https://www.juraprofi.de/images/product_images/popup_images/dosier-einstellregler-fuer-ecm-casa-speciale-kaffeemuehle-r3.jpg|https://www.juraprofi.de/images/product_images/popup_images/dosier-einstellregler-fuer-ecm-casa-speciale-kaffeemuehle-r3-1.jpg|https://www.juraprofi.de/images/product_images/popup_images/dosier-einstellregler-fuer-ecm-casa-speciale-kaffeemuehle-r3-2.jpg|https://www.juraprofi.de/images/product_images/popup_images/dosier-einstellregler-fuer-ecm-casa-speciale-kaffeemuehle-r3-3.jpg</t>
+  </si>
+  <si>
+    <t>Casa Speciale Kaffeemühle</t>
   </si>
 </sst>
 </file>
@@ -359,22 +398,62 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:3">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:3">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
   <si>
     <t>ссылка</t>
   </si>
@@ -26,13 +26,19 @@
     <t>совместимость</t>
   </si>
   <si>
+    <t>название</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Pumpe-und-Fluidsystem/Anschluss-T-Form-1-8-fuer-Espressomaschine::20013.html</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/images/product_images/popup_images/anschluss-t-form-1-8-fuer-espressomaschine-15455.jpg|https://www.juraprofi.de/images/product_images/popup_images/anschluss-t-form-1-8-fuer-espressomaschine-15455-1.jpg</t>
   </si>
   <si>
-    <t>Barista,Casa IV,Casa V,Classika II,Classika PID,Compact HX-2,Controvento,Controvento Due,Elektronika II Profi,Elektronika Profi Due,Mechanika III,Mechanika IV,Mechanika Profi,Mechanika V Slim,Synchronika,Technika III,Technika IV,Technika Profi,Technika V Profi PID,Pro 300,Pro 500,Pro 600,Pro 700,Pro 800,0960 Carola (Einkreis),0975 La Certa (Einkreis),0980 Andreja,0980 Andreja (NEW),0980 Milano,0981 Rubino,0985 Aquila (NEW),0987 Rapida (Hebelmaschine),0990 Anita,0992 QM 67,0995 Vetrano,0995 Vetrano (NEW),0996 Achille (Hebelmaschine),04005 Silvano,04100 Pippa,Appartamento,Cellini,Cellini,Cinquantotto,Giotto,Mozzafiato,R58,R60</t>
+    <t>Barista, Casa IV, Casa V, Classika II, Classika PID, Compact HX-2, Controvento, Controvento Due, Elektronika II Profi, Elektronika Profi Due, Mechanika III, Mechanika IV, Mechanika Profi, Mechanika V Slim, Synchronika, Technika III, Technika IV, Technika Profi, Technika V Profi PID, Pro 300, Pro 500, Pro 600, Pro 700, Pro 800, 0960 Carola (Einkreis), 0975 La Certa (Einkreis), 0980 Andreja, 0980 Andreja (NEW), 0980 Milano, 0981 Rubino, 0985 Aquila (NEW), 0987 Rapida (Hebelmaschine), 0990 Anita, 0992 QM 67, 0995 Vetrano, 0995 Vetrano (NEW), 0996 Achille (Hebelmaschine), 04005 Silvano, 04100 Pippa, Appartamento, Cellini, Cellini, Cinquantotto, Giotto, Mozzafiato, R58, R60</t>
+  </si>
+  <si>
+    <t>Anschluss T-Form 1/8" für Espressomaschine</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/DeLonghi-Ersatzteile/Wassertank/Abdeckung-Wassertank-silber-fuer-DeLonghi-Perfecta-Evo::17096.html</t>
@@ -44,13 +50,19 @@
     <t>ESAM 428.80.SB Perfecta Evo</t>
   </si>
   <si>
+    <t>Abdeckung Wassertank silber für DeLonghi Perfecta Evo</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Dichtungen/Teflondichtung-Dampfkessel-ECM-und-Profitec-Espressomaschine::19247.html</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/images/product_images/popup_images/teflondichtung-dampfkessel-ecm-und-profitec-espressomaschine-c469900779.jpg|https://www.juraprofi.de/images/product_images/popup_images/teflondichtung-dampfkessel-ecm-und-profitec-espressomaschine-c469900779-1.jpg</t>
   </si>
   <si>
-    <t>Compact HX-2,Controvento Due,Pro 800</t>
+    <t>Compact HX-2, Controvento Due, Pro 800</t>
+  </si>
+  <si>
+    <t>Teflondichtung Dampfkessel ECM und Profitec Espressomaschine</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Kaffeemuehle/Dosier-Einstellregler-fuer-ECM-Casa-Speciale-Kaffeemuehle::18825.html</t>
@@ -60,6 +72,9 @@
   </si>
   <si>
     <t>Casa Speciale Kaffeemühle</t>
+  </si>
+  <si>
+    <t>Dosier Einstellregler für ECM Casa Speciale Kaffeemühle</t>
   </si>
 </sst>
 </file>
@@ -398,10 +413,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -411,49 +426,64 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>ссылка</t>
   </si>
@@ -29,6 +29,9 @@
     <t>название</t>
   </si>
   <si>
+    <t>описание</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Pumpe-und-Fluidsystem/Anschluss-T-Form-1-8-fuer-Espressomaschine::20013.html</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
     <t>Anschluss T-Form 1/8" für Espressomaschine</t>
   </si>
   <si>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Barista&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa V&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika II&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika PID&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika II Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika Profi Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika V Slim&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Synchronika&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika V Profi PID&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 300&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 500&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 600&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 700&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Quickmill&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0960 Carola (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0975 La Certa (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Milano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0981 Rubino&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0985 Aquila (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0987 Rapida (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0990 Anita&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0992 QM 67&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0996 Achille (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04005 Silvano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04100 Pippa&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Rocket&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Appartamento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cinquantotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Giotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mozzafiato&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R58&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R60&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/DeLonghi-Ersatzteile/Wassertank/Abdeckung-Wassertank-silber-fuer-DeLonghi-Perfecta-Evo::17096.html</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
     <t>Abdeckung Wassertank silber für DeLonghi Perfecta Evo</t>
   </si>
   <si>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;DeLonghi&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;ESAM 428.80.SB Perfecta Evo&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Dichtungen/Teflondichtung-Dampfkessel-ECM-und-Profitec-Espressomaschine::19247.html</t>
   </si>
   <si>
@@ -65,6 +74,9 @@
     <t>Teflondichtung Dampfkessel ECM und Profitec Espressomaschine</t>
   </si>
   <si>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Kaffeemuehle/Dosier-Einstellregler-fuer-ECM-Casa-Speciale-Kaffeemuehle::18825.html</t>
   </si>
   <si>
@@ -75,6 +87,9 @@
   </si>
   <si>
     <t>Dosier Einstellregler für ECM Casa Speciale Kaffeemühle</t>
+  </si>
+  <si>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa Speciale Kaffeemühle&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
@@ -413,10 +428,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -429,61 +444,76 @@
       <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="0" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -44,7 +44,7 @@
     <t>Anschluss T-Form 1/8" für Espressomaschine</t>
   </si>
   <si>
-    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Barista&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa V&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika II&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika PID&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika II Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika Profi Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika V Slim&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Synchronika&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika V Profi PID&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 300&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 500&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 600&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 700&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Quickmill&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0960 Carola (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0975 La Certa (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Milano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0981 Rubino&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0985 Aquila (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0987 Rapida (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0990 Anita&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0992 QM 67&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0996 Achille (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04005 Silvano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04100 Pippa&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Rocket&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Appartamento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cinquantotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Giotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mozzafiato&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R58&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R60&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Barista&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa V&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika II&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Classika PID&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika II Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Elektronika Profi Due&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mechanika V Slim&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Synchronika&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika III&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika IV&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika Profi&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Technika V Profi PID&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 300&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 500&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 600&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 700&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Quickmill&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0960 Carola (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0975 La Certa (Einkreis)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Andreja (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0980 Milano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0981 Rubino&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0985 Aquila (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0987 Rapida (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0990 Anita&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0992 QM 67&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0995 Vetrano (NEW)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;0996 Achille (Hebelmaschine)&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04005 Silvano&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;04100 Pippa&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Rocket&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Appartamento&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cellini&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Cinquantotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Giotto&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Mozzafiato&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R58&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;R60&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/DeLonghi-Ersatzteile/Wassertank/Abdeckung-Wassertank-silber-fuer-DeLonghi-Perfecta-Evo::17096.html</t>
@@ -59,7 +59,7 @@
     <t>Abdeckung Wassertank silber für DeLonghi Perfecta Evo</t>
   </si>
   <si>
-    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;DeLonghi&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;ESAM 428.80.SB Perfecta Evo&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;DeLonghi&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;ESAM 428.80.SB Perfecta Evo&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Dichtungen/Teflondichtung-Dampfkessel-ECM-und-Profitec-Espressomaschine::19247.html</t>
@@ -74,7 +74,7 @@
     <t>Teflondichtung Dampfkessel ECM und Profitec Espressomaschine</t>
   </si>
   <si>
-    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Compact HX-2&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Controvento Due&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;Profitec&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Pro 800&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
     <t>https://www.juraprofi.de/ECM-Ersatzteile/Kaffeemuehle/Dosier-Einstellregler-fuer-ECM-Casa-Speciale-Kaffeemuehle::18825.html</t>
@@ -89,7 +89,7 @@
     <t>Dosier Einstellregler für ECM Casa Speciale Kaffeemühle</t>
   </si>
   <si>
-    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa Speciale Kaffeemühle&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+    <t>&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;div&gt;Данная запчасть подходит для ремонта кофемашины:&lt;/div&gt;&lt;div&gt;&amp;nbsp;&lt;/div&gt;&lt;h2 style="margin: 0px 0px 15px; padding: 0px; font-size: 18px; color: rgb(0, 76, 179); font-weight: 400; line-height: 24px;"&gt;&lt;strong&gt;ECM&lt;/strong&gt;&lt;/h2&gt;&lt;ul style="margin: 0px 0px 13px 15px; padding-right: 0px; padding-left: 0px; color: rgb(88, 88, 90);  line-height: 18px;"&gt;&gt;&lt;li&gt;&lt;span style="color: rgb(105, 105, 105);"&gt;Casa Speciale Kaffeemühle&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
